--- a/output_excel/q1_4.xlsx
+++ b/output_excel/q1_4.xlsx
@@ -471,13 +471,13 @@
         <v>2.55</v>
       </c>
       <c r="D2" t="n">
-        <v>2.549999999996825</v>
+        <v>2.55</v>
       </c>
       <c r="E2" t="n">
-        <v>2.549992488797007</v>
+        <v>2.55</v>
       </c>
       <c r="F2" t="n">
-        <v>2.28747328814592</v>
+        <v>2.2875</v>
       </c>
     </row>
     <row r="3">
@@ -488,16 +488,16 @@
         <v>2.55</v>
       </c>
       <c r="C3" t="n">
-        <v>2.549999999997772</v>
+        <v>2.55</v>
       </c>
       <c r="D3" t="n">
-        <v>2.54999984728174</v>
+        <v>2.55</v>
       </c>
       <c r="E3" t="n">
-        <v>2.548607101927899</v>
+        <v>2.5486</v>
       </c>
       <c r="F3" t="n">
-        <v>2.065973012222165</v>
+        <v>2.066</v>
       </c>
     </row>
     <row r="4">
@@ -505,19 +505,19 @@
         <v>600</v>
       </c>
       <c r="B4" t="n">
-        <v>2.549999999991511</v>
+        <v>2.55</v>
       </c>
       <c r="C4" t="n">
-        <v>2.54999998449559</v>
+        <v>2.55</v>
       </c>
       <c r="D4" t="n">
-        <v>2.549963111217629</v>
+        <v>2.55</v>
       </c>
       <c r="E4" t="n">
-        <v>2.534246408121131</v>
+        <v>2.5342</v>
       </c>
       <c r="F4" t="n">
-        <v>1.884747416220156</v>
+        <v>1.8847</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +525,19 @@
         <v>900</v>
       </c>
       <c r="B5" t="n">
-        <v>2.549999995971056</v>
+        <v>2.55</v>
       </c>
       <c r="C5" t="n">
-        <v>2.549998797203509</v>
+        <v>2.55</v>
       </c>
       <c r="D5" t="n">
-        <v>2.549516826691331</v>
+        <v>2.5495</v>
       </c>
       <c r="E5" t="n">
-        <v>2.504106776637122</v>
+        <v>2.5041</v>
       </c>
       <c r="F5" t="n">
-        <v>1.759831932962827</v>
+        <v>1.7598</v>
       </c>
     </row>
     <row r="6">
@@ -545,19 +545,19 @@
         <v>1200</v>
       </c>
       <c r="B6" t="n">
-        <v>2.54999981567637</v>
+        <v>2.55</v>
       </c>
       <c r="C6" t="n">
-        <v>2.549982974257098</v>
+        <v>2.55</v>
       </c>
       <c r="D6" t="n">
-        <v>2.547797978916378</v>
+        <v>2.5478</v>
       </c>
       <c r="E6" t="n">
-        <v>2.464717781689223</v>
+        <v>2.4647</v>
       </c>
       <c r="F6" t="n">
-        <v>1.662257867247234</v>
+        <v>1.6623</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +565,19 @@
         <v>1500</v>
       </c>
       <c r="B7" t="n">
-        <v>2.549997467512733</v>
+        <v>2.55</v>
       </c>
       <c r="C7" t="n">
-        <v>2.549897673171114</v>
+        <v>2.5499</v>
       </c>
       <c r="D7" t="n">
-        <v>2.543976446621104</v>
+        <v>2.544</v>
       </c>
       <c r="E7" t="n">
-        <v>2.421144004404099</v>
+        <v>2.4211</v>
       </c>
       <c r="F7" t="n">
-        <v>1.581550217203186</v>
+        <v>1.5816</v>
       </c>
     </row>
     <row r="8">
@@ -585,19 +585,19 @@
         <v>1800</v>
       </c>
       <c r="B8" t="n">
-        <v>2.549982908737666</v>
+        <v>2.55</v>
       </c>
       <c r="C8" t="n">
-        <v>2.549625596841533</v>
+        <v>2.5496</v>
       </c>
       <c r="D8" t="n">
-        <v>2.537626483191388</v>
+        <v>2.5376</v>
       </c>
       <c r="E8" t="n">
-        <v>2.376224649135131</v>
+        <v>2.3762</v>
       </c>
       <c r="F8" t="n">
-        <v>1.512467624136292</v>
+        <v>1.5125</v>
       </c>
     </row>
   </sheetData>
